--- a/Configs/Datas/__tables__.xlsx
+++ b/Configs/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3A7ABB-0FC0-44C9-B805-C6CF73A19780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9D6916-7B14-4314-A001-CB0FA52918C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -101,13 +101,68 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
+  </si>
+  <si>
+    <t>ZZZ.TbCharacterBase</t>
+  </si>
+  <si>
+    <t>ZZZ.TbCharacterEnergy</t>
+  </si>
+  <si>
+    <t>ZZZ.TbCharacterElement</t>
+  </si>
+  <si>
+    <t>ZZZ.TbCharacterSpecial</t>
+  </si>
+  <si>
+    <t>ZZZ.CharacterBase</t>
+  </si>
+  <si>
+    <t>ZZZ.CharacterEnergy</t>
+  </si>
+  <si>
+    <t>ZZZ.CharacterElement</t>
+  </si>
+  <si>
+    <t>ZZZ.CharacterSpecial</t>
+  </si>
+  <si>
+    <t>characterId</t>
+  </si>
+  <si>
+    <t>角色基础攻防表</t>
+  </si>
+  <si>
+    <t>角色能量与喧响表</t>
+  </si>
+  <si>
+    <t>角色元素与抗性表</t>
+  </si>
+  <si>
+    <t>角色独有机制与Buff表</t>
+  </si>
+  <si>
+    <t>Base@ZZZ.CharacterAttribute.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy@ZZZ.CharacterAttribute.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Element@ZZZ.CharacterAttribute.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Special@ZZZ.CharacterAttribute.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +180,15 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -160,11 +224,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -443,13 +510,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="25.875" customWidth="1"/>
+    <col min="3" max="3" width="27.375" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -541,6 +608,86 @@
       </c>
       <c r="K3" s="1" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I7" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
